--- a/review/abilities/workbooks/11_Ancestry_Elf.xlsx
+++ b/review/abilities/workbooks/11_Ancestry_Elf.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Traits" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pairs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Compare" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Change Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traits" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pairs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compare" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Traits'!$A$4:$L$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Traits'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pairs'!$A$4:$G$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Pairs'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,7 +82,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="007F6000"/>
+      <color rgb="00006100"/>
       <sz val="9"/>
     </font>
     <font>
@@ -116,7 +116,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -188,7 +188,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -225,19 +225,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -744,7 +731,7 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Best default Speed; Footfall and Dream are excellent exploration traits; A Lifetime Ago gives the character a deep story hook. Grace is simple and always useful.</t>
+          <t>Best default Speed; Footfall now ignores natural woodland difficult terrain and adds +1 Speed in woods; Dream is an excellent rest trait; A Lifetime Ago lets the character call on ancestral knowledge once per day. Grace is simple and always useful.</t>
         </is>
       </c>
     </row>
@@ -758,7 +745,7 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Several traits are woodland- or rest-specific; A Lifetime Ago needs campaign buy-in. Grace is mechanically identical to Human Road in the Blood. The ancestry has no social trait beyond lore.</t>
+          <t>Footfall is strong in woodland but does nothing outside it; several other traits are woodland- or rest-specific. A Lifetime Ago is broad but limited to once per day. Grace is the straightforward +1 Speed option. The ancestry has no social trait beyond lore.</t>
         </is>
       </c>
     </row>
@@ -772,7 +759,7 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Broaden Wood Whispers to any natural environment or add a non-woodland clause. Give Grace a small elven rider to differentiate it from Human Speed. Clarify the scope of 'earlier age'.</t>
+          <t>Nature’s Whispers is approved as the simple nature-reading trait; no further change. Give Grace a small elven rider to differentiate it from Human Speed.</t>
         </is>
       </c>
     </row>
@@ -818,7 +805,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock</t>
+          <t>Hard as Bedrock</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -867,7 +854,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Combat, Defense, Exploration, Social, Support, Utility</t>
+          <t>Combat, Defense, Exploration, Social, Utility</t>
         </is>
       </c>
     </row>
@@ -884,12 +871,12 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Never Quite Finished, Road in the Blood</t>
+          <t>Never Quite Finished</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Movement, Social, Support, Utility</t>
+          <t>Defense, Exploration, Social, Utility</t>
         </is>
       </c>
     </row>
@@ -930,17 +917,17 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Two pairs of ancestry traits are mechanically identical: Stubborn as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'.</t>
+          <t>The baseline duplicate stat traits have been differentiated: Hard as Bedrock (+1 maximum HP), Never Quite Finished (+1 maximum HP and a death-mark Boon), Grace of the Elder Folk (+1 Speed) and Adaptable (+1 DP per level).</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Keep the stat but add a small ancestry-specific rider: Dwarf +1 to stabilization or reduce Bleeding after a rest; Human a travel/endurance clause; Elf ignore 1 square of difficult terrain once per scene; Human speed a forced-march benefit.</t>
+          <t>No further action; keep the differentiation.</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1138,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="41.5" customHeight="1">
+    <row r="5" ht="66.5" customHeight="1">
       <c r="A5" s="7" t="n">
         <v>1</v>
       </c>
@@ -1167,12 +1154,12 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Natural undergrowth does not increase the cost of your voluntary movement; other difficult terrain is unchanged.</t>
+          <t>In woodlands or forests, ignore difficult terrain and gain +1 Speed.</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Natural undergrowth does not increase the cost of your voluntary movement. Other difficult terrain, forced movement and occupied-square rules are unchanged.</t>
+          <t>In woodlands and forests, you ignore difficult terrain. This includes difficult terrain caused by natural terrain or obstacles, such as roots, undergrowth, fallen leaves and uneven natural ground. Your Speed increases by 1 while you are in woodlands, forests or similar wooded terrain.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1187,12 +1174,12 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Clean mobility trait with a clear scope. It makes the Elf feel at home in the wild without granting full difficult-terrain immunity.</t>
+          <t>Explicit woodland mobility: ignore natural difficult terrain and gain +1 Speed. Strong in forests, inert outside them.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether magical undergrowth is affected (it should not be) and whether the trait applies while carrying another creature.</t>
+          <t>Approved: explicit ‘ignore difficult terrain’ wording plus +1 Speed in wooded terrain.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr"/>
@@ -1219,12 +1206,12 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Choose one place or community you knew in an earlier age; gain 1 Boon to Knowledge or Reason rolls recalling its history, people or construction.</t>
+          <t>Once per day, before a Knowledge or Reason roll, call on ancestral knowledge to gain 1 Boon to that roll.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Choose one place or community you knew in an earlier age. Gain 1 Boon to Knowledge or Reason rolls recalling its history, people or construction. The DA can tell you what you genuinely witnessed without a roll; memory reveals no events you never knew.</t>
+          <t>Once per day, before you make a Knowledge or Reason roll, you may call on the knowledge of your ancestors to gain 1 Boon to that roll.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -1239,12 +1226,12 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Strong lore trait with a built-in story hook. It rewards campaign buy-in and gives the Elf a long memory.</t>
+          <t>Ancestral memory trait: one Boon per day to Knowledge or Reason. Simple, broad, and tied to the Elves’ interconnected minds rather than one chosen place.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Define 'earlier age' and whether the bonus applies to people and places that no longer exist. Add a note that the DA can share genuinely witnessed facts without a roll.</t>
+          <t>Approved: replaced place/community memory with a once-per-day ancestral knowledge Boon. Name unchanged.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr"/>
@@ -1255,13 +1242,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
+    <row r="7" ht="41.5" customHeight="1">
       <c r="A7" s="7" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>The Wood Whispers</t>
+          <t>Nature’s Whispers</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1271,17 +1258,17 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>In woodland, gain 1 Boon to a consequential roll interpreting living signs of nearby disturbance.</t>
+          <t>Gain 1 Boon to a roll interpreting living signs.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>In woodland, gain 1 Boon to a consequential roll interpreting living signs of nearby disturbance. The signs can indicate a general direction, not an unseen creature’s exact square; this does not bypass Hidden.</t>
+          <t>Gain 1 Boon to a roll interpreting living signs.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Exploration</t>
+          <t>Exploration, Utility</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1291,12 +1278,12 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Narrow but evocative. It shines in a wilderness campaign and does little in a city or dungeon.</t>
+          <t>Simple, broad nature-reading trait: one Boon on any roll interpreting living signs. No terrain restriction, no extra clause.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Allow any natural environment (not only woodland) or permit cultivated land at a Bane. Clarify that it gives direction, not an exact hidden square.</t>
+          <t>Approved: simplified to one Boon on any roll interpreting living signs and renamed Nature’s Whispers.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr"/>
@@ -1343,7 +1330,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Simple, always useful, and easy to understand. It is mechanically identical to Human Road in the Blood.</t>
+          <t>Simple, always useful, and easy to understand. It is the straightforward +1 Speed option now that Human has Adaptable.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -1359,7 +1346,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="41.5" customHeight="1">
       <c r="A9" s="7" t="n">
         <v>5</v>
       </c>
@@ -1375,12 +1362,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Rest in a quiet waking reverie instead of sleeping, remaining aware of nearby ordinary sights and sounds.</t>
+          <t>Rest in waking reverie instead of sleeping; aware of nearby ordinary sights and sounds; counts as sleep for rest and recovery.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>You may rest in a quiet waking reverie instead of sleeping, remaining aware of nearby ordinary sights and sounds. It grants no automatic detection, extra downtime work, shorter treatment interval or Grit recovery. Magical Asleep still works normally.</t>
+          <t>You may rest in a quiet waking reverie instead of sleeping. You remain aware of nearby ordinary sights and sounds. The reverie counts as sleep for rest and recovery.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1395,12 +1382,12 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Strong for watch rotations and camp scenes. It is also a nice cultural detail.</t>
+          <t>Rest and awareness trait: useful for watch rotations and camp scenes. The reverie counts as sleep and grants ordinary awareness.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Define 'ordinary danger' and whether the reverie counts as sleep for exhaustion and recovery. Clarify that magical Asleep still works normally (text says yes).</t>
+          <t>Approved: clarified rest/recovery and ordinary awareness; removed the Magical Asleep sentence.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr"/>
@@ -1428,15 +1415,12 @@
       <formula>J5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>J5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>J5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="J5:J9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1556,12 +1540,12 @@
     <row r="6" ht="41.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Footfall on the Leaves + The Wood Whispers</t>
+          <t>Footfall on the Leaves + Nature’s Whispers</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Movement, Exploration</t>
+          <t>Movement, Exploration, Utility</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1571,7 +1555,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Footfall on the Leaves leans exploration, movement; The Wood Whispers leans exploration. Together they cover movement, exploration.</t>
+          <t>Footfall on the Leaves leans exploration, movement; Nature’s Whispers leans exploration, utility. Together they cover movement, exploration, utility.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1643,7 +1627,7 @@
     <row r="9" ht="41.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>A Lifetime Ago + The Wood Whispers</t>
+          <t>A Lifetime Ago + Nature’s Whispers</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1658,7 +1642,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>A Lifetime Ago leans social, utility; The Wood Whispers leans exploration. Together they cover exploration, social, utility.</t>
+          <t>A Lifetime Ago leans social, utility; Nature’s Whispers leans exploration, utility. Together they cover exploration, social, utility.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1730,12 +1714,12 @@
     <row r="12" ht="41.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>The Wood Whispers + Grace of the Elder Folk</t>
+          <t>Nature’s Whispers + Grace of the Elder Folk</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Movement, Exploration</t>
+          <t>Movement, Exploration, Utility</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1745,7 +1729,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>The Wood Whispers leans exploration; Grace of the Elder Folk leans movement. Together they cover movement, exploration.</t>
+          <t>Nature’s Whispers leans exploration, utility; Grace of the Elder Folk leans movement. Together they cover movement, exploration, utility.</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1759,12 +1743,12 @@
     <row r="13" ht="41.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>The Wood Whispers + Dream beneath the Stars</t>
+          <t>Nature’s Whispers + Dream beneath the Stars</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Exploration, Support</t>
+          <t>Exploration, Support, Utility</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1774,12 +1758,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>The Wood Whispers leans exploration; Dream beneath the Stars leans exploration, support. Together they cover exploration, support.</t>
+          <t>Nature’s Whispers leans exploration, utility; Dream beneath the Stars leans exploration, support. Together they cover exploration, support, utility.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>No obvious anti-synergy; choose for the character story and the campaign's mix of combat, exploration and social scenes.</t>
+          <t>Both traits are campaign-dependent. Confirm the campaign will feature the relevant terrain, craft or social scenes.</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
@@ -1831,15 +1815,12 @@
       <formula>F5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>F5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>F5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1956,7 +1937,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Stubborn as Bedrock</t>
+          <t>Hard as Bedrock</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2045,7 +2026,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Combat, Defense, Exploration, Social, Support, Utility</t>
+          <t>Combat, Defense, Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2082,12 +2063,12 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Never Quite Finished, Road in the Blood</t>
+          <t>Never Quite Finished</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Defense, Exploration, Movement, Social, Support, Utility</t>
+          <t>Defense, Exploration, Social, Utility</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -2118,7 +2099,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>• Stubborn as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'. The mechanics are identical; only the fiction differs (F12).</t>
+          <t>• Hard as Bedrock and Never Quite Finished are both '+1 maximum HP'; Grace of the Elder Folk and Road in the Blood are both '+1 base Speed'. The mechanics are identical; only the fiction differs (F12).</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2182,12 +2163,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="11" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="11" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -2268,30 +2248,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2315,7 +2290,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -2335,7 +2309,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -2355,7 +2328,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -2375,7 +2347,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -2395,7 +2366,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -2415,7 +2385,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -2435,7 +2404,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -2455,7 +2423,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -2475,7 +2442,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -2495,7 +2461,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -2515,7 +2480,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -2535,23 +2499,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
